--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -9797,13 +9797,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -14875,7 +14875,7 @@
         <v>2</v>
       </c>
       <c r="R138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S138" s="9" t="n">
         <v>1</v>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,11 @@
       <c r="AB2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1028,7 +1032,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2163,7 +2171,11 @@
       <c r="AB14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3092,7 +3104,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3298,7 +3314,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3605,7 +3625,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3807,7 +3831,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3908,7 +3936,11 @@
       <c r="AB31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4728,7 +4760,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5556,7 +5592,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5657,7 +5697,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -7095,7 +7139,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -9660,7 +9708,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9761,7 +9813,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -10068,7 +10124,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10791,7 +10851,11 @@
       <c r="AB98" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC98" s="4" t="inlineStr"/>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -12649,7 +12713,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12750,7 +12818,11 @@
       <c r="AB117" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC117" s="4" t="inlineStr"/>
+      <c r="AC117" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -13061,7 +13133,11 @@
       <c r="AB120" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13162,7 +13238,11 @@
       <c r="AB121" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC121" s="4" t="inlineStr"/>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13469,7 +13549,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13881,7 +13965,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14083,7 +14171,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14705,7 +14797,11 @@
       <c r="AB136" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC136" s="4" t="inlineStr"/>
+      <c r="AC136" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -14806,7 +14902,11 @@
       <c r="AB137" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC137" s="4" t="inlineStr"/>
+      <c r="AC137" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -15008,7 +15108,11 @@
       <c r="AB139" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC139" s="4" t="inlineStr"/>
+      <c r="AC139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -15622,7 +15726,11 @@
       <c r="AB145" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC145" s="4" t="inlineStr"/>
+      <c r="AC145" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -15723,7 +15831,11 @@
       <c r="AB146" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC146" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -15925,7 +16037,11 @@
       <c r="AB148" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC148" s="4" t="inlineStr"/>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -16236,7 +16352,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -17266,7 +17386,11 @@
       <c r="AB161" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC161" s="4" t="inlineStr"/>
+      <c r="AC161" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 55 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 48 clubs short</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2683,8 +2683,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6201,8 +6201,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6512,8 +6512,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14578,8 +14578,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14718,7 +14718,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14788,8 +14788,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -16104,7 +16104,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q151" s="9" t="n">
         <v>0</v>
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16860,8 +16860,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -17142,7 +17142,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17797,8 +17797,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -19332,7 +19332,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19563,7 +19563,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -20058,7 +20058,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -20091,7 +20091,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -20223,7 +20223,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -20289,7 +20289,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$179</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -831,24 +831,24 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>28680682</v>
+        <v>1279299</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Synechron UK</t>
+          <t>Hamwic Speakers</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -900,32 +900,38 @@
       <c r="S2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="9" t="n">
-        <v>0</v>
+      <c r="T2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>0</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
+      <c r="X2" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z2" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AB2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -939,15 +945,15 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1279299</v>
+        <v>7713357</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Hamwic Speakers</t>
+          <t>Shilling Speakers</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -961,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -988,31 +994,31 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q3" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="9" t="n">
-        <v>0</v>
+      <c r="S3" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="9" t="n">
-        <v>0</v>
+      <c r="U3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X3" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -1044,15 +1050,15 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>7713357</v>
+        <v>5774</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Shilling Speakers</t>
+          <t>Solent Speakers Club</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1066,17 +1072,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1093,22 +1099,22 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" s="10" t="n">
-        <v>1</v>
+      <c r="S4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
         <v>2</v>
@@ -1117,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="9" t="n">
         <v>0</v>
@@ -1129,11 +1135,11 @@
         <v>1</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -1149,11 +1155,11 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5774</v>
+        <v>2685904</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Solent Speakers Club</t>
+          <t>Spinnaker Speakers</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -1171,17 +1177,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -1198,10 +1204,10 @@
         </is>
       </c>
       <c r="P5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
@@ -1221,8 +1227,8 @@
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="10" t="n">
-        <v>4</v>
+      <c r="X5" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1234,11 +1240,11 @@
         <v>1</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -1250,19 +1256,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2685904</v>
+        <v>4670783</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Spinnaker Speakers</t>
+          <t>Ascot &amp; Bracknell Speakers</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1276,17 +1282,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -1312,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="9" t="n">
         <v>0</v>
@@ -1320,14 +1326,14 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="9" t="n">
-        <v>1</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -1339,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
@@ -1359,11 +1365,11 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4670783</v>
+        <v>8471</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Ascot &amp; Bracknell Speakers</t>
+          <t>Reading Speakers Club</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -1381,13 +1387,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1408,7 +1414,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1417,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="9" t="n">
         <v>0</v>
@@ -1429,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X7" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1444,11 +1450,11 @@
         <v>1</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -1464,15 +1470,15 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8471</v>
+        <v>5257932</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Reading Speakers Club</t>
+          <t>Reading Verizon Toastmasters</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1486,17 +1492,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1513,7 +1519,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>0</v>
@@ -1531,31 +1537,27 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="10" t="n">
-        <v>1</v>
+      <c r="Z8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1569,15 +1571,15 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5257932</v>
+        <v>7850144</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Reading Verizon Toastmasters</t>
+          <t>Verizon EMEA Online Toastmasters Club</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1591,13 +1593,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1629,32 +1631,32 @@
       <c r="S9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="9" t="n">
-        <v>0</v>
+      <c r="T9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
+      <c r="X9" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9" s="4" t="inlineStr"/>
     </row>
@@ -1670,15 +1672,15 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7850144</v>
+        <v>3124015</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Verizon EMEA Online Toastmasters Club</t>
+          <t>Wokingham Speakers</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1692,13 +1694,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1730,8 +1732,8 @@
       <c r="S10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="10" t="n">
-        <v>1</v>
+      <c r="T10" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -1743,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1755,9 +1757,13 @@
         <v>1</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1767,19 +1773,19 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3124015</v>
+        <v>1163131</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Wokingham Speakers</t>
+          <t>Casterbridge Speakers</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1793,17 +1799,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -1831,20 +1837,20 @@
       <c r="S11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -1856,11 +1862,11 @@
         <v>1</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -1876,15 +1882,15 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1163131</v>
+        <v>595108</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Casterbridge Speakers</t>
+          <t>Chaseside Speakers Toastmasters Club - J.P.Morgan Chase empl</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1898,17 +1904,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1936,21 +1942,21 @@
       <c r="S12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="T12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
@@ -1961,13 +1967,9 @@
         <v>1</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1981,15 +1983,15 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>595108</v>
+        <v>1768164</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Chaseside Speakers Toastmasters Club - J.P.Morgan Chase empl</t>
+          <t>Ferndown Speakers</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2003,17 +2005,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
@@ -2039,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>0</v>
@@ -2047,14 +2049,14 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>2</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
@@ -2066,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC13" s="4" t="inlineStr"/>
     </row>
@@ -2082,15 +2084,15 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1768164</v>
+        <v>742</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ferndown Speakers</t>
+          <t>Hallmark Speakers</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2104,17 +2106,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2131,19 +2133,19 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
@@ -2152,10 +2154,10 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2167,9 +2169,13 @@
         <v>1</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2183,15 +2189,15 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>742</v>
+        <v>5877910</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Hallmark Speakers</t>
+          <t>Salisbury Online Speakers</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2205,17 +2211,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2232,25 +2238,25 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q15" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="10" t="n">
-        <v>1</v>
+      <c r="T15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2268,11 +2274,11 @@
         <v>1</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -2288,15 +2294,15 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5877910</v>
+        <v>28675954</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Salisbury Online Speakers</t>
+          <t>Wealth CDIO Toastmasters Club</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2310,13 +2316,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2340,7 +2346,7 @@
         <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -2360,26 +2366,22 @@
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X16" s="10" t="n">
-        <v>7</v>
+      <c r="X16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="10" t="n">
-        <v>1</v>
+      <c r="Z16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2389,19 +2391,19 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28675954</v>
+        <v>3599330</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Wealth CDIO Toastmasters Club</t>
+          <t>Basingstoke Speakers</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2415,13 +2417,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2442,45 +2444,49 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="9" t="n">
-        <v>0</v>
+      <c r="X17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2494,15 +2500,15 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3599330</v>
+        <v>1348895</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Basingstoke Speakers</t>
+          <t>Microsoft Speakers Club</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2516,17 +2522,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="7" t="n">
@@ -2543,7 +2549,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2560,14 +2566,14 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="10" t="n">
-        <v>4</v>
+      <c r="V18" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -2579,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
@@ -2599,15 +2605,15 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1348895</v>
+        <v>2965</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Microsoft Speakers Club</t>
+          <t>Newbury Speakers Club</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2621,17 +2627,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
@@ -2648,7 +2654,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2665,14 +2671,14 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>1</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -2704,11 +2710,11 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2965</v>
+        <v>7932757</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Newbury Speakers Club</t>
+          <t>Speakers Denn</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -2726,17 +2732,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="7" t="n">
@@ -2753,49 +2759,45 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2809,15 +2811,15 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7932757</v>
+        <v>9090</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Speakers Denn</t>
+          <t>Wessex Speakers Club</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2831,17 +2833,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
@@ -2869,34 +2871,38 @@
       <c r="S21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="9" t="n">
-        <v>0</v>
+      <c r="T21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2906,19 +2912,19 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9090</v>
+        <v>1249064</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Wessex Speakers Club</t>
+          <t>Armada Speakers</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2932,17 +2938,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
@@ -2970,14 +2976,14 @@
       <c r="S22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="10" t="n">
-        <v>1</v>
+      <c r="T22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -2995,13 +3001,9 @@
         <v>1</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3015,15 +3017,15 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1249064</v>
+        <v>4547336</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Armada Speakers</t>
+          <t>Bath Spa Toastmasters</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3037,13 +3039,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3064,10 +3066,10 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>0</v>
@@ -3075,20 +3077,20 @@
       <c r="S23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="9" t="n">
-        <v>0</v>
+      <c r="T23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -3100,9 +3102,13 @@
         <v>1</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3116,11 +3122,11 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4547336</v>
+        <v>5812194</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Bath Spa Toastmasters</t>
+          <t>Bristol Central Speakers</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -3138,13 +3144,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3165,25 +3171,25 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="9" t="n">
-        <v>0</v>
+      <c r="S24" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="10" t="n">
-        <v>1</v>
+      <c r="U24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3201,11 +3207,11 @@
         <v>1</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -3221,11 +3227,11 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5812194</v>
+        <v>8580</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Bristol Central Speakers</t>
+          <t>Northavon Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -3243,13 +3249,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3269,32 +3275,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="10" t="n">
+      <c r="S25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3306,11 +3312,11 @@
         <v>1</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC25" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -3326,15 +3332,15 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8580</v>
+        <v>907029</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Northavon Speakers Toastmasters Club</t>
+          <t>South West Speakers</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3348,13 +3354,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3374,17 +3380,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P26" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="10" t="n">
-        <v>2</v>
+      <c r="P26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="9" t="n">
         <v>0</v>
@@ -3398,8 +3404,8 @@
       <c r="W26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X26" s="10" t="n">
-        <v>6</v>
+      <c r="X26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
@@ -3411,11 +3417,11 @@
         <v>1</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC26" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -3431,15 +3437,15 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>907029</v>
+        <v>5161</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>South West Speakers</t>
+          <t>Thamesdown Speakers Club</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3453,17 +3459,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3497,14 +3503,14 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>1</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3516,31 +3522,27 @@
         <v>1</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5161</v>
+        <v>2390</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Thamesdown Speakers Club</t>
+          <t>Berkeley Square Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -3558,13 +3560,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5</v>
+        <v>-19</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3585,31 +3587,31 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="10" t="n">
-        <v>4</v>
+      <c r="V28" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="X28" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
@@ -3621,9 +3623,13 @@
         <v>1</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3637,15 +3643,15 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2390</v>
+        <v>6963045</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Berkeley Square Speakers Toastmasters Club</t>
+          <t>Centurion Toastmasters</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3659,17 +3665,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3686,49 +3692,45 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X29" s="10" t="n">
-        <v>6</v>
+      <c r="X29" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="10" t="n">
-        <v>1</v>
+      <c r="Z29" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3742,15 +3744,15 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6963045</v>
+        <v>7951</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Centurion Toastmasters</t>
+          <t>London Corinthians Toastmasters</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3764,13 +3766,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
@@ -3791,7 +3793,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -3808,28 +3810,32 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>0</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3843,15 +3849,15 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7951</v>
+        <v>5235</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>London Corinthians Toastmasters</t>
+          <t>London Olympians Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3865,13 +3871,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3901,10 +3907,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
@@ -3913,10 +3919,10 @@
         <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="9" t="n">
         <v>2</v>
+      </c>
+      <c r="X31" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -3948,15 +3954,15 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5235</v>
+        <v>1095711</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>London Olympians Speakers Toastmasters Club</t>
+          <t>Polish Your Polish</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3970,17 +3976,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="7" t="n">
@@ -4006,22 +4012,22 @@
         <v>0</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="10" t="n">
-        <v>4</v>
+      <c r="V32" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="10" t="n">
-        <v>7</v>
+      <c r="X32" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
@@ -4033,13 +4039,9 @@
         <v>1</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4053,11 +4055,11 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1095711</v>
+        <v>28678633</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Polish Your Polish</t>
+          <t>Toastmasters at the BBC</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
@@ -4075,17 +4077,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
@@ -4102,7 +4104,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4120,13 +4122,13 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>3</v>
+      <c r="X33" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -4138,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC33" s="4" t="inlineStr"/>
     </row>
@@ -4150,19 +4152,19 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>28678633</v>
+        <v>5513601</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters at the BBC</t>
+          <t>Clapham Connectors</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4176,17 +4178,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="7" t="n">
@@ -4203,7 +4205,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -4220,28 +4222,32 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="10" t="n">
+      <c r="V34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W34" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="X34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Y34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4255,15 +4261,15 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5513601</v>
+        <v>28679471</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Clapham Connectors</t>
+          <t>Excalibur Online Global Speakers</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4277,13 +4283,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4304,10 +4310,10 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4321,32 +4327,28 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="10" t="n">
+      <c r="V35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W35" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC35" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4360,15 +4362,15 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>28679471</v>
+        <v>2684362</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Excalibur Online Global Speakers</t>
+          <t>Experience French</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4382,13 +4384,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4409,10 +4411,10 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q36" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4427,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4445,9 +4447,13 @@
         <v>1</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4461,15 +4467,15 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>2684362</v>
+        <v>7064444</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Experience French</t>
+          <t>Legacy Speakers Brixton</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4483,17 +4489,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
@@ -4510,10 +4516,10 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4528,13 +4534,13 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X37" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37" s="9" t="n">
         <v>0</v>
@@ -4546,11 +4552,11 @@
         <v>1</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC37" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -4566,15 +4572,15 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>7064444</v>
+        <v>7814710</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Legacy Speakers Brixton</t>
+          <t>LSBU Public Speakers Club</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4588,17 +4594,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="7" t="n">
@@ -4639,25 +4645,21 @@
         <v>0</v>
       </c>
       <c r="X38" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="10" t="n">
-        <v>1</v>
+      <c r="Z38" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC38" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4671,15 +4673,15 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>7814710</v>
+        <v>5257</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>LSBU Public Speakers Club</t>
+          <t>Tube Talk Toastmasters</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4693,13 +4695,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4731,8 +4733,8 @@
       <c r="S39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
@@ -4744,21 +4746,25 @@
         <v>0</v>
       </c>
       <c r="X39" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4768,19 +4774,19 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>5257</v>
+        <v>5987771</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Tube Talk Toastmasters</t>
+          <t>Central London Toastmasters</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4794,13 +4800,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4838,11 +4844,11 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>0</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>4</v>
@@ -4857,11 +4863,11 @@
         <v>1</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC40" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -4877,15 +4883,15 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>5987771</v>
+        <v>28678882</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Central London Toastmasters</t>
+          <t>Ciso Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4899,13 +4905,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4943,14 +4949,14 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="10" t="n">
-        <v>4</v>
+      <c r="V41" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X41" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>0</v>
@@ -4962,13 +4968,9 @@
         <v>1</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC41" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4982,11 +4984,11 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>28678882</v>
+        <v>835375</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Ciso Speakers Toastmasters</t>
+          <t>Early Bird Speakers</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -5004,13 +5006,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5055,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -5067,9 +5069,13 @@
         <v>1</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5083,11 +5089,11 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>835375</v>
+        <v>9079</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Early Bird Speakers</t>
+          <t>Excalibur Speakers</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -5105,13 +5111,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
+        <v>-23</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5141,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0</v>
@@ -5150,13 +5156,13 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X43" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
@@ -5168,11 +5174,11 @@
         <v>1</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC43" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -5188,15 +5194,15 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>9079</v>
+        <v>2078451</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Excalibur Speakers</t>
+          <t>Society Speakers</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5210,13 +5216,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5237,28 +5243,28 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="9" t="n">
-        <v>0</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W44" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>7</v>
@@ -5273,13 +5279,9 @@
         <v>1</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC44" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5289,19 +5291,19 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2078451</v>
+        <v>4144038</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Society Speakers</t>
+          <t>104 London Debaters</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5315,17 +5317,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
@@ -5342,32 +5344,32 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="10" t="n">
+      <c r="V45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
@@ -5378,9 +5380,13 @@
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5394,15 +5400,15 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>4144038</v>
+        <v>2277701</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>104 London Debaters</t>
+          <t>Kings Speakers</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5416,17 +5422,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5461,19 +5467,19 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X46" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="10" t="n">
-        <v>1</v>
+      <c r="Z46" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5499,15 +5505,15 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>2277701</v>
+        <v>674907</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Kings Speakers</t>
+          <t>London Cardinals</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5521,17 +5527,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
@@ -5548,7 +5554,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5566,29 +5572,29 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X47" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC47" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -5604,15 +5610,15 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>674907</v>
+        <v>4138266</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>London Cardinals</t>
+          <t>London Victorians</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5629,10 +5635,10 @@
         <v>41</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>-15</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5653,16 +5659,16 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -5670,14 +5676,14 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>1</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X48" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
@@ -5709,11 +5715,11 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>4138266</v>
+        <v>28675589</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>London Victorians</t>
+          <t>PA Consulting London</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -5731,10 +5737,10 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>2</v>
@@ -5760,30 +5766,30 @@
       <c r="P49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W49" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="X49" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R49" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
@@ -5794,11 +5800,11 @@
         <v>1</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC49" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5820,15 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>28675589</v>
+        <v>6843951</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>PA Consulting London</t>
+          <t>Zig-Zag Toastmasters</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5836,17 +5842,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5887,25 +5893,21 @@
         <v>0</v>
       </c>
       <c r="X50" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="10" t="n">
-        <v>1</v>
+      <c r="Z50" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC50" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5915,19 +5917,19 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>6843951</v>
+        <v>4141</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Zig-Zag Toastmasters</t>
+          <t>Grosvenor Square Speakers</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5941,13 +5943,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5986,19 +5988,19 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X51" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6020,15 +6022,15 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>4141</v>
+        <v>7305510</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Grosvenor Square Speakers</t>
+          <t>GSK House Toastmasters Club</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6042,13 +6044,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6056,11 +6058,11 @@
         </is>
       </c>
       <c r="M52" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr">
@@ -6086,11 +6088,11 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W52" s="9" t="n">
-        <v>0</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W52" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X52" s="9" t="n">
         <v>3</v>
@@ -6101,11 +6103,11 @@
       <c r="Z52" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA52" s="10" t="n">
-        <v>1</v>
+      <c r="AA52" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC52" s="4" t="inlineStr"/>
     </row>
@@ -6121,15 +6123,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>7305510</v>
+        <v>3149</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>GSK House Toastmasters Club</t>
+          <t>Holborn Speakers</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6143,13 +6145,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6157,11 +6159,11 @@
         </is>
       </c>
       <c r="M53" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr">
@@ -6181,20 +6183,20 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>0</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X53" s="9" t="n">
-        <v>3</v>
+      <c r="X53" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
@@ -6202,13 +6204,17 @@
       <c r="Z53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA53" s="9" t="n">
-        <v>0</v>
+      <c r="AA53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6222,15 +6228,15 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>3149</v>
+        <v>4495118</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Holborn Speakers</t>
+          <t>Paddington Toastmasters</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6244,10 +6250,10 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>4</v>
@@ -6271,10 +6277,10 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -6282,8 +6288,8 @@
       <c r="S54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="10" t="n">
-        <v>1</v>
+      <c r="T54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
@@ -6292,10 +6298,10 @@
         <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X54" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -6307,11 +6313,11 @@
         <v>1</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6327,15 +6333,15 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>4495118</v>
+        <v>28678189</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Paddington Toastmasters</t>
+          <t>VMO2 Toastmasters Club</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6349,17 +6355,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="7" t="n">
@@ -6376,10 +6382,10 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
@@ -6393,54 +6399,50 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="10" t="n">
-        <v>4</v>
+      <c r="V55" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="10" t="n">
-        <v>1</v>
+      <c r="Z55" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC55" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>28678189</v>
+        <v>1417626</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>VMO2 Toastmasters Club</t>
+          <t>Bloomsbury Speakers</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6454,17 +6456,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="7" t="n">
@@ -6498,28 +6500,32 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>0</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>3</v>
+      <c r="X56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6533,15 +6539,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1417626</v>
+        <v>4169140</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Bloomsbury Speakers</t>
+          <t>City Limits Speakers</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6555,13 +6561,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J57" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J57" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="K57" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6582,16 +6588,16 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="9" t="n">
         <v>0</v>
@@ -6599,8 +6605,8 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="10" t="n">
-        <v>4</v>
+      <c r="V57" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6618,11 +6624,11 @@
         <v>1</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC57" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6638,15 +6644,15 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>4169140</v>
+        <v>4713088</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>City Limits Speakers</t>
+          <t>GS London Toastmasters Club</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6660,25 +6666,25 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr">
@@ -6687,16 +6693,16 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -6705,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="10" t="n">
-        <v>4</v>
+      <c r="X58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6719,17 +6725,13 @@
       <c r="Z58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA58" s="10" t="n">
-        <v>1</v>
+      <c r="AA58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6743,15 +6745,15 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>4713088</v>
+        <v>28677278</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>GS London Toastmasters Club</t>
+          <t>LSEG London Toastmasters Club</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6765,13 +6767,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6779,11 +6781,11 @@
         </is>
       </c>
       <c r="M59" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr">
@@ -6792,7 +6794,7 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="9" t="n">
         <v>0</v>
@@ -6815,8 +6817,8 @@
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
+      <c r="X59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6824,13 +6826,17 @@
       <c r="Z59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA59" s="9" t="n">
-        <v>0</v>
+      <c r="AA59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6844,15 +6850,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>28677278</v>
+        <v>28677680</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>LSEG London Toastmasters Club</t>
+          <t>Toastmasters @ Markel</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6866,13 +6872,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6880,11 +6886,11 @@
         </is>
       </c>
       <c r="M60" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr">
@@ -6893,7 +6899,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6911,13 +6917,13 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="10" t="n">
-        <v>4</v>
+      <c r="X60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6925,17 +6931,13 @@
       <c r="Z60" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA60" s="10" t="n">
-        <v>1</v>
+      <c r="AA60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC60" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6945,19 +6947,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>28677680</v>
+        <v>6816509</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters @ Markel</t>
+          <t>Accenture Speakers (London)</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6971,13 +6973,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6985,11 +6987,11 @@
         </is>
       </c>
       <c r="M61" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr">
@@ -6998,10 +7000,10 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -7016,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X61" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
@@ -7030,11 +7032,11 @@
       <c r="Z61" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA61" s="9" t="n">
-        <v>0</v>
+      <c r="AA61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC61" s="4" t="inlineStr"/>
     </row>
@@ -7050,15 +7052,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>6816509</v>
+        <v>6718778</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Accenture Speakers (London)</t>
+          <t>Bloomberg London Toastmasters</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7072,13 +7074,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7099,16 +7101,16 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7116,14 +7118,14 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>1</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="X62" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
@@ -7135,9 +7137,13 @@
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7151,15 +7157,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>6718778</v>
+        <v>28678359</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Bloomberg London Toastmasters</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7173,25 +7179,25 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-55</v>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O63" s="8" t="inlineStr">
@@ -7209,7 +7215,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -7217,32 +7223,28 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="10" t="n">
-        <v>4</v>
+      <c r="V63" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X63" s="10" t="n">
-        <v>5</v>
+      <c r="X63" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="10" t="n">
-        <v>1</v>
+      <c r="Z63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC63" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7256,15 +7258,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>28678359</v>
+        <v>28677260</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>I&amp;C Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7278,25 +7280,25 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O64" s="8" t="inlineStr">
@@ -7334,14 +7336,14 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC64" s="4" t="inlineStr"/>
     </row>
@@ -7357,11 +7359,11 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>28677260</v>
+        <v>28679861</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>I&amp;C Toastmasters Club</t>
+          <t>JP Morgan EMEA Solutions</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -7379,17 +7381,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M65" s="7" t="n">
@@ -7442,7 +7444,7 @@
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="4" t="inlineStr"/>
     </row>
@@ -7458,11 +7460,11 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>28679861</v>
+        <v>28680682</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>JP Morgan EMEA Solutions</t>
+          <t>Synechron UK</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7480,10 +7482,10 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>0</v>
@@ -7537,14 +7539,12 @@
         <v>0</v>
       </c>
       <c r="Z66" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB66" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7783,13 +7783,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>9</v>
+        <v>-22</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>7</v>
@@ -7888,17 +7888,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
@@ -7993,13 +7993,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
@@ -8094,17 +8094,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="7" t="n">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8195,13 +8195,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8239,8 +8239,8 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>3</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8401,17 +8401,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="7" t="n">
@@ -8506,13 +8506,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8611,17 +8611,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
@@ -8658,8 +8658,8 @@
       <c r="V77" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W77" s="9" t="n">
-        <v>2</v>
+      <c r="W77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>17</v>
+        <v>-39</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>4</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="X78" s="9" t="n">
         <v>2</v>
@@ -8817,13 +8817,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8922,17 +8922,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -8967,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -9124,13 +9124,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9326,17 +9326,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="7" t="n">
@@ -9370,11 +9370,11 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>3</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>4</v>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9475,8 +9475,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>2</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9637,13 +9637,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9681,11 +9681,11 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
+      <c r="V87" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W87" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W87" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>4</v>
@@ -9742,13 +9742,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9847,13 +9847,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9894,8 +9894,8 @@
       <c r="V89" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W89" s="9" t="n">
-        <v>0</v>
+      <c r="W89" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9952,17 +9952,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="7" t="n">
@@ -10158,13 +10158,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10263,13 +10263,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10310,8 +10310,8 @@
       <c r="V93" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W93" s="9" t="n">
-        <v>1</v>
+      <c r="W93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10368,13 +10368,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10412,11 +10412,11 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>3</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>5</v>
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10679,13 +10679,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10723,8 +10723,8 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>3</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10784,13 +10784,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10885,13 +10885,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>59</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q99" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q99" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>5</v>
@@ -10990,17 +10990,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -11091,13 +11091,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11192,17 +11192,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -11240,7 +11240,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>4</v>
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>4</v>
@@ -11398,13 +11398,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11503,13 +11503,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11608,13 +11608,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11709,13 +11709,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11810,17 +11810,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="7" t="n">
@@ -11840,7 +11840,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11854,8 +11854,8 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>3</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -12020,17 +12020,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="7" t="n">
@@ -12125,13 +12125,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
@@ -12226,17 +12226,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="7" t="n">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12331,17 +12331,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="7" t="n">
@@ -12436,17 +12436,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="7" t="n">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12484,7 +12484,7 @@
         <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>5</v>
@@ -12541,17 +12541,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="7" t="n">
@@ -12586,7 +12586,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12646,13 +12646,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>1</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12747,17 +12747,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="7" t="n">
@@ -12852,13 +12852,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12957,13 +12957,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13062,13 +13062,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13106,11 +13106,11 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>3</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>5</v>
@@ -13167,13 +13167,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>4</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -13272,13 +13272,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13377,13 +13377,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13421,11 +13421,11 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>3</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X123" s="9" t="n">
         <v>2</v>
@@ -13482,13 +13482,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -13583,13 +13583,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>7</v>
@@ -13688,17 +13688,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -13793,13 +13793,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="8" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13894,17 +13894,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13939,7 +13939,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13999,13 +13999,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -14104,13 +14104,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14205,13 +14205,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>6</v>
+        <v>-15</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>4</v>
@@ -14415,17 +14415,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
@@ -14516,17 +14516,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="7" t="n">
@@ -14621,17 +14621,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="7" t="n">
@@ -14726,17 +14726,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="7" t="n">
@@ -14771,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14831,17 +14831,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="7" t="n">
@@ -14936,17 +14936,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15041,13 +15041,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -15067,14 +15067,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P139" s="9" t="n">
-        <v>3</v>
+      <c r="P139" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q139" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R139" s="9" t="n">
-        <v>1</v>
+      <c r="R139" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S139" s="9" t="n">
         <v>1</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15348,13 +15348,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15392,8 +15392,8 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>2</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L143" s="8" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15554,17 +15554,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="7" t="n">
@@ -15760,13 +15760,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15865,13 +15865,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15912,8 +15912,8 @@
       <c r="V147" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W147" s="9" t="n">
-        <v>3</v>
+      <c r="W147" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>7</v>
@@ -15970,17 +15970,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="7" t="n">
@@ -16071,13 +16071,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16281,17 +16281,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16386,13 +16386,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16430,8 +16430,8 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>2</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16491,17 +16491,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="7" t="n">
@@ -16536,7 +16536,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16596,17 +16596,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -16701,13 +16701,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L155" s="8" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16802,13 +16802,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L156" s="8" t="inlineStr">
         <is>
@@ -16846,11 +16846,11 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="9" t="n">
-        <v>2</v>
+      <c r="V156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>6</v>
@@ -16903,17 +16903,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L157" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="7" t="n">
@@ -17008,13 +17008,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>4</v>
       </c>
       <c r="W159" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>6</v>
@@ -17214,17 +17214,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="7" t="n">
@@ -17244,7 +17244,7 @@
         <v>2</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
@@ -17259,7 +17259,7 @@
         <v>0</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -17315,13 +17315,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>4</v>
       </c>
       <c r="W161" s="10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>6</v>
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q162" s="9" t="n">
         <v>1</v>
@@ -17525,17 +17525,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L163" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="7" t="n">
@@ -17570,7 +17570,7 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17630,17 +17630,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L164" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="7" t="n">
@@ -17674,11 +17674,11 @@
       <c r="U164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V164" s="9" t="n">
-        <v>2</v>
+      <c r="V164" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X164" s="10" t="n">
         <v>6</v>
@@ -17735,13 +17735,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>4</v>
       </c>
       <c r="W165" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>7</v>
@@ -17840,13 +17840,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17941,13 +17941,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L167" s="8" t="inlineStr">
         <is>
@@ -17985,11 +17985,11 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>0</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>5</v>
@@ -17997,8 +17997,8 @@
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="10" t="n">
         <v>1</v>
@@ -18042,17 +18042,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L168" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="7" t="n">
@@ -18147,13 +18147,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
@@ -18248,17 +18248,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L170" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M170" s="7" t="n">
@@ -18335,7 +18335,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18349,13 +18349,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>7</v>
+        <v>-12</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18396,8 +18396,8 @@
       <c r="V171" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W171" s="9" t="n">
-        <v>3</v>
+      <c r="W171" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X171" s="9" t="n">
         <v>0</v>
@@ -18454,13 +18454,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" s="8" t="inlineStr">
         <is>
@@ -18555,13 +18555,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18656,13 +18656,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L174" s="8" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>0</v>
       </c>
       <c r="V174" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
@@ -18757,13 +18757,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L175" s="8" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>0</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -18844,7 +18844,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18905,8 +18905,8 @@
       <c r="V176" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W176" s="9" t="n">
-        <v>1</v>
+      <c r="W176" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X176" s="10" t="n">
         <v>7</v>
@@ -18949,7 +18949,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18963,13 +18963,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -19007,11 +19007,11 @@
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="9" t="n">
-        <v>1</v>
+      <c r="V177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X177" s="10" t="n">
         <v>6</v>
@@ -19068,13 +19068,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>1</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -19173,13 +19173,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -19256,7 +19256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -19320,25 +19320,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -19347,7 +19347,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -19358,20 +19358,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -19380,7 +19380,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -19391,20 +19391,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -19413,7 +19413,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -19424,20 +19424,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -19446,7 +19446,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -19457,20 +19457,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -19479,25 +19479,25 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -19512,7 +19512,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -19545,7 +19545,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -19556,20 +19556,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -19578,7 +19578,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -19589,20 +19589,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -19622,47 +19622,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -19674,10 +19674,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -19688,29 +19688,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -19721,17 +19721,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -19740,10 +19740,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -19754,17 +19754,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -19773,10 +19773,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -19787,62 +19787,62 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -19853,20 +19853,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -19886,20 +19886,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -19919,29 +19919,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -19952,26 +19952,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
@@ -19985,20 +19985,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -20007,31 +20007,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -20051,14 +20051,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -20084,20 +20084,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -20117,14 +20117,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -20150,20 +20150,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -20172,28 +20172,28 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -20205,7 +20205,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -20216,20 +20216,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -20238,7 +20238,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -20249,20 +20249,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -20271,7 +20271,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -20304,7 +20304,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -20337,25 +20337,25 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -20381,29 +20381,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -20414,29 +20414,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -20447,14 +20447,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>1.17</v>
+        <v>2.33</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -20472,41 +20472,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>6</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>6</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I37"/>
+  <autoFilter ref="A1:I36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1694,17 +1694,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-15</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>2</v>
@@ -2106,17 +2106,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2154,7 +2154,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3188,8 +3188,8 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-19</v>
+        <v>-15</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3871,13 +3871,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -4178,13 +4178,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X34" s="9" t="n">
         <v>1</v>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-19</v>
+        <v>-10</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4847,8 +4847,8 @@
       <c r="V40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W40" s="9" t="n">
-        <v>1</v>
+      <c r="W40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>4</v>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5050,8 +5050,8 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>3</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5216,13 +5216,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>7</v>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -6973,13 +6973,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -7074,13 +7074,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>5</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8506,13 +8506,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-39</v>
+        <v>-37</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>4</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X78" s="9" t="n">
         <v>2</v>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8922,17 +8922,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -8966,8 +8966,8 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>3</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="9" t="n">
         <v>0</v>
@@ -9847,13 +9847,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>5</v>
@@ -9952,13 +9952,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10158,13 +10158,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10202,11 +10202,11 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>3</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>4</v>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10603,8 +10603,8 @@
       <c r="P96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" s="9" t="n">
-        <v>1</v>
+      <c r="Q96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10784,13 +10784,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10828,11 +10828,11 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>2</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" s="9" t="n">
         <v>3</v>
@@ -10885,13 +10885,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>59</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -11192,17 +11192,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -11240,7 +11240,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>4</v>
@@ -12852,13 +12852,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -14205,13 +14205,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14415,13 +14415,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>5</v>
@@ -14621,13 +14621,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14936,17 +14936,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14980,11 +14980,11 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>2</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>7</v>
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15076,8 +15076,8 @@
       <c r="R139" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S139" s="9" t="n">
-        <v>1</v>
+      <c r="S139" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T139" s="10" t="n">
         <v>1</v>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15554,17 +15554,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M144" s="7" t="n">
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -15865,13 +15865,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -17315,13 +17315,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>4</v>
       </c>
       <c r="W161" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>6</v>
@@ -17735,13 +17735,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17941,13 +17941,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L167" s="8" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>5</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -19068,13 +19068,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -19112,8 +19112,8 @@
       <c r="U178" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V178" s="9" t="n">
-        <v>3</v>
+      <c r="V178" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -19173,13 +19173,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -19413,7 +19413,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -19464,7 +19464,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -19563,7 +19563,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -19794,7 +19794,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -19809,7 +19809,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -19860,7 +19860,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19893,7 +19893,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19926,7 +19926,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19941,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -20190,7 +20190,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -20205,7 +20205,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -20238,7 +20238,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -20454,7 +20454,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>

--- a/docs/d/91/inyear.xlsx
+++ b/docs/d/91/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>0</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>2</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2052,8 +2052,8 @@
       <c r="V13" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>3</v>
+      <c r="W13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>5</v>
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2938,13 +2938,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3039,17 +3039,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
@@ -3083,8 +3083,8 @@
       <c r="U23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>3</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="P25" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q25" s="10" t="n">
         <v>2</v>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3595,8 +3595,8 @@
       <c r="R28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="9" t="n">
-        <v>1</v>
+      <c r="S28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T28" s="10" t="n">
         <v>1</v>
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4489,13 +4489,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5361,8 +5361,8 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5466,8 +5466,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5554,11 +5554,11 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
       </c>
@@ -5571,8 +5571,8 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>3</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -6044,13 +6044,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X52" s="9" t="n">
         <v>3</v>
@@ -6145,13 +6145,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6973,13 +6973,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -7017,8 +7017,8 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>2</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7783,13 +7783,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>7</v>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7888,13 +7888,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7926,8 +7926,8 @@
       <c r="S70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -8195,17 +8195,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="7" t="n">
@@ -8243,7 +8243,7 @@
         <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-23</v>
+        <v>-14</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8506,13 +8506,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8550,8 +8550,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8611,17 +8611,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
@@ -8659,7 +8659,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8712,13 +8712,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-37</v>
+        <v>-30</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>4</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="X78" s="9" t="n">
         <v>2</v>
@@ -9124,13 +9124,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>5</v>
@@ -9938,7 +9938,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -10008,8 +10008,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10299,7 +10299,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
         <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -11192,13 +11192,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11340,8 +11340,8 @@
       <c r="V103" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W103" s="9" t="n">
-        <v>3</v>
+      <c r="W103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>4</v>
@@ -11398,13 +11398,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
@@ -11443,7 +11443,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11503,13 +11503,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12226,13 +12226,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12436,17 +12436,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L114" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M114" s="7" t="n">
@@ -12747,13 +12747,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -13197,7 +13197,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13272,13 +13272,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="10" t="n">
         <v>2</v>
@@ -13823,7 +13823,7 @@
         <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -14104,13 +14104,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>5</v>
@@ -14310,13 +14310,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14516,13 +14516,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" s="9" t="n">
         <v>0</v>
@@ -15865,13 +15865,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
@@ -16101,13 +16101,13 @@
         <v>0</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" s="10" t="n">
         <v>1</v>
@@ -16281,17 +16281,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -16329,7 +16329,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>5</v>
@@ -16701,13 +16701,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L155" s="8" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -17214,13 +17214,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
@@ -17315,13 +17315,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>4</v>
       </c>
       <c r="W161" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>6</v>
@@ -17630,13 +17630,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X164" s="10" t="n">
         <v>6</v>
@@ -17735,13 +17735,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>4</v>
       </c>
       <c r="W165" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>7</v>
@@ -18349,13 +18349,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>4</v>
       </c>
       <c r="W171" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X171" s="9" t="n">
         <v>0</v>
@@ -18555,13 +18555,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>4</v>
       </c>
       <c r="W173" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X173" s="10" t="n">
         <v>4</v>
@@ -18757,13 +18757,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L175" s="8" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>0</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>4</v>
       </c>
       <c r="W176" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X176" s="10" t="n">
         <v>7</v>
@@ -19398,7 +19398,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -19464,7 +19464,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -19479,7 +19479,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -19497,7 +19497,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19695,7 +19695,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19728,7 +19728,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -19761,7 +19761,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19776,7 +19776,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -19860,7 +19860,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19959,7 +19959,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -20304,7 +20304,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
